--- a/ValueSet-hiv-d-de371.xlsx
+++ b/ValueSet-hiv-d-de371.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from itech-uw Concept" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from HIV-DAK Concepts" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://fhir.org/guides/itech-uw/ValueSet/hiv-d-de371</t>
+    <t>http://fhir.org/guides/who/hiv-dak/ValueSet/hiv-d-de371</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-31T07:49:07+00:00</t>
+    <t>2024-05-31T12:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -168,7 +168,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://fhir.org/guides/itech-uw/who-smart-hiv-dak/CodeSystem/concept-codes</t>
+    <t>http://fhir.org/guides/who/hiv-dak/CodeSystem/HIV-DAKConcepts</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-hiv-d-de371.xlsx
+++ b/ValueSet-hiv-d-de371.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-31T12:57:23+00:00</t>
+    <t>2024-06-06T18:19:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-hiv-d-de371.xlsx
+++ b/ValueSet-hiv-d-de371.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T18:19:00+00:00</t>
+    <t>2024-06-06T18:29:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
